--- a/datos/Paschenairedistancia10cm.xlsx
+++ b/datos/Paschenairedistancia10cm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7815"/>
+    <workbookView windowWidth="20490" windowHeight="7815" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,14 +38,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="0.0000_ "/>
-    <numFmt numFmtId="179" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="0.00000_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,10 +54,102 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -69,9 +161,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -79,127 +170,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -214,31 +207,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,150 +388,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,40 +405,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -477,6 +437,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -487,6 +471,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -508,158 +501,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1007,183 +999,183 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4">
-        <v>0.0072</v>
+        <v>0.00072</v>
       </c>
       <c r="B3">
         <v>1352</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4">
-        <v>0.008</v>
+        <v>0.0008</v>
       </c>
       <c r="B4">
         <v>748</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4">
-        <v>0.0098</v>
+        <v>0.00098</v>
       </c>
       <c r="B5">
         <v>587</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4">
-        <v>0.012</v>
+        <v>0.0012</v>
       </c>
       <c r="B6">
         <v>342</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4">
-        <v>0.014</v>
+        <v>0.0014</v>
       </c>
       <c r="B7">
         <v>346</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4">
-        <v>0.017</v>
+        <v>0.0017</v>
       </c>
       <c r="B8">
         <v>314</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4">
-        <v>0.022</v>
+        <v>0.0022</v>
       </c>
       <c r="B9">
         <v>300</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4">
-        <v>0.023</v>
+        <v>0.0023</v>
       </c>
       <c r="B10">
         <v>292</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="4">
-        <v>0.027</v>
+        <v>0.0027</v>
       </c>
       <c r="B11">
         <v>308</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4">
-        <v>0.029</v>
+        <v>0.0029</v>
       </c>
       <c r="B12">
         <v>319.8</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4">
-        <v>0.039</v>
+        <v>0.0039</v>
       </c>
       <c r="B13">
         <v>302.8</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="4">
-        <v>0.039</v>
+        <v>0.0039</v>
       </c>
       <c r="B14">
         <v>347</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="4">
-        <v>0.046</v>
+        <v>0.0046</v>
       </c>
       <c r="B15">
         <v>356</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4">
-        <v>0.052</v>
+        <v>0.0052</v>
       </c>
       <c r="B16">
         <v>364</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="4">
-        <v>0.054</v>
+        <v>0.0054</v>
       </c>
       <c r="B17">
         <v>374.9</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4">
-        <v>0.069</v>
+        <v>0.0069</v>
       </c>
       <c r="B18">
         <v>394.2</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4">
-        <v>0.075</v>
+        <v>0.0075</v>
       </c>
       <c r="B19">
         <v>411</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4">
-        <v>0.083</v>
+        <v>0.0083</v>
       </c>
       <c r="B20">
         <v>426</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4">
-        <v>0.092</v>
+        <v>0.0092</v>
       </c>
       <c r="B21">
         <v>435</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4">
-        <v>0.12</v>
+        <v>0.012</v>
       </c>
       <c r="B22">
         <v>491</v>
       </c>
-      <c r="D22" s="5"/>
+      <c r="D22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1194,8 +1186,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="37.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="11.2857142857143" customWidth="1"/>
@@ -1215,141 +1207,158 @@
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3">
-        <v>0.0068</v>
-      </c>
-      <c r="B3" s="2">
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>0.00068</v>
+      </c>
+      <c r="B3" s="1">
         <v>1760</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3">
-        <v>0.0076</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
+        <v>0.00076</v>
+      </c>
+      <c r="B4" s="1">
         <v>789</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3">
-        <v>0.009</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>0.0009</v>
+      </c>
+      <c r="B5" s="1">
         <v>474</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3">
-        <v>0.0093</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>0.00093</v>
+      </c>
+      <c r="B6" s="1">
         <v>420</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
+        <v>0.00097</v>
+      </c>
+      <c r="B7" s="1">
+        <v>430</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="B8" s="1">
+        <v>396</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
+        <v>0.0013</v>
+      </c>
+      <c r="B9" s="1">
+        <v>343</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
+        <v>0.0015</v>
+      </c>
+      <c r="B10" s="1">
+        <v>338</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
+        <v>0.0018</v>
+      </c>
+      <c r="B11" s="1">
+        <v>318</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
+        <v>0.0022</v>
+      </c>
+      <c r="B12" s="1">
+        <v>320</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2">
+        <v>0.0029</v>
+      </c>
+      <c r="B13" s="1">
+        <v>316</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2">
+        <v>0.0036</v>
+      </c>
+      <c r="B14" s="1">
+        <v>356</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2">
+        <v>0.0042</v>
+      </c>
+      <c r="B15" s="1">
+        <v>358</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2">
+        <v>0.0056</v>
+      </c>
+      <c r="B16" s="1">
+        <v>370</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2">
+        <v>0.0069</v>
+      </c>
+      <c r="B17" s="1">
+        <v>414</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2">
+        <v>0.0089</v>
+      </c>
+      <c r="B18" s="1">
+        <v>453</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2">
         <v>0.0097</v>
       </c>
-      <c r="B7" s="2">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="B8" s="2">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="3">
-        <v>0.013</v>
-      </c>
-      <c r="B9" s="2">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="B10" s="2">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3">
-        <v>0.018</v>
-      </c>
-      <c r="B11" s="2">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="3">
-        <v>0.022</v>
-      </c>
-      <c r="B12" s="2">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="3">
-        <v>0.029</v>
-      </c>
-      <c r="B13" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="3">
-        <v>0.036</v>
-      </c>
-      <c r="B14" s="2">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="3">
-        <v>0.042</v>
-      </c>
-      <c r="B15" s="2">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="3">
-        <v>0.056</v>
-      </c>
-      <c r="B16" s="2">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="3">
-        <v>0.069</v>
-      </c>
-      <c r="B17" s="2">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="3">
-        <v>0.089</v>
-      </c>
-      <c r="B18" s="2">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="3">
-        <v>0.097</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>490</v>
       </c>
+      <c r="D19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1382,122 +1391,122 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
-        <v>0.0077</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="A3" s="1">
+        <v>0.00077</v>
+      </c>
+      <c r="B3" s="1">
         <v>779</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
-        <v>0.0084</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="A4" s="1">
+        <v>0.00084</v>
+      </c>
+      <c r="B4" s="1">
         <v>590</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
-        <v>0.0089</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="A5" s="1">
+        <v>0.00089</v>
+      </c>
+      <c r="B5" s="1">
         <v>492</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
-        <v>0.0091</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="A6" s="1">
+        <v>0.00091</v>
+      </c>
+      <c r="B6" s="1">
         <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
-        <v>0.0096</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="A7" s="1">
+        <v>0.00096</v>
+      </c>
+      <c r="B7" s="1">
         <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
-        <v>0.012</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="A8" s="1">
+        <v>0.0012</v>
+      </c>
+      <c r="B8" s="1">
         <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
-        <v>0.015</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="A9" s="1">
+        <v>0.0015</v>
+      </c>
+      <c r="B9" s="1">
         <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>0.019</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="A10" s="1">
+        <v>0.0019</v>
+      </c>
+      <c r="B10" s="1">
         <v>316</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>0.022</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="A11" s="1">
+        <v>0.0022</v>
+      </c>
+      <c r="B11" s="1">
         <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>0.029</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="A12" s="1">
+        <v>0.0029</v>
+      </c>
+      <c r="B12" s="1">
         <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>0.035</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="A13" s="1">
+        <v>0.0035</v>
+      </c>
+      <c r="B13" s="1">
         <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>0.052</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="A14" s="1">
+        <v>0.0052</v>
+      </c>
+      <c r="B14" s="1">
         <v>390</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
-        <v>0.066</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="A15" s="1">
+        <v>0.0066</v>
+      </c>
+      <c r="B15" s="1">
         <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
-        <v>0.078</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="A16" s="1">
+        <v>0.0078</v>
+      </c>
+      <c r="B16" s="1">
         <v>420</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
-        <v>0.095</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="A17" s="1">
+        <v>0.0095</v>
+      </c>
+      <c r="B17" s="1">
         <v>443</v>
       </c>
     </row>
